--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/7.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/7.xlsx
@@ -426,13 +426,13 @@
         <v>-15.45086567745568</v>
       </c>
       <c r="E2">
-        <v>-10.89683285357272</v>
+        <v>-8.901238513294572</v>
       </c>
       <c r="F2">
-        <v>-1.369439860492355</v>
+        <v>-2.383716395505971</v>
       </c>
       <c r="G2">
-        <v>-8.768732505265488</v>
+        <v>-10.67578881589035</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.30673007916758</v>
       </c>
       <c r="E3">
-        <v>-11.35717487882245</v>
+        <v>-9.870476862104274</v>
       </c>
       <c r="F3">
-        <v>-1.34246618134059</v>
+        <v>-2.25162898733466</v>
       </c>
       <c r="G3">
-        <v>-8.576326909068586</v>
+        <v>-10.2196982674905</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.11725760675803</v>
       </c>
       <c r="E4">
-        <v>-11.95125632694071</v>
+        <v>-11.22869754275084</v>
       </c>
       <c r="F4">
-        <v>-1.402442708064197</v>
+        <v>-2.483883419098643</v>
       </c>
       <c r="G4">
-        <v>-8.507484114579441</v>
+        <v>-9.835708090390433</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.89412219385335</v>
       </c>
       <c r="E5">
-        <v>-13.6997952392564</v>
+        <v>-12.54863450413655</v>
       </c>
       <c r="F5">
-        <v>-1.322440220039858</v>
+        <v>-1.761300966267283</v>
       </c>
       <c r="G5">
-        <v>-8.540225409962833</v>
+        <v>-9.659262634238358</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.6355276099457</v>
       </c>
       <c r="E6">
-        <v>-13.3531813102353</v>
+        <v>-13.09914297535301</v>
       </c>
       <c r="F6">
-        <v>-1.163206508771999</v>
+        <v>-2.018309513342543</v>
       </c>
       <c r="G6">
-        <v>-8.116955610039316</v>
+        <v>-8.965597406303788</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.3514819647672</v>
       </c>
       <c r="E7">
-        <v>-14.54964942780189</v>
+        <v>-12.49945074793925</v>
       </c>
       <c r="F7">
-        <v>-1.07031344644894</v>
+        <v>-1.71131366460531</v>
       </c>
       <c r="G7">
-        <v>-7.823753833808223</v>
+        <v>-10.47575903331651</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.04952400502915</v>
       </c>
       <c r="E8">
-        <v>-15.07296894107629</v>
+        <v>-12.5317161252439</v>
       </c>
       <c r="F8">
-        <v>-0.8637586024277503</v>
+        <v>-2.150021583211896</v>
       </c>
       <c r="G8">
-        <v>-7.984384813919201</v>
+        <v>-9.726493193049878</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.73666567779756</v>
       </c>
       <c r="E9">
-        <v>-15.48186297312487</v>
+        <v>-13.94111309065114</v>
       </c>
       <c r="F9">
-        <v>-0.9697116955824803</v>
+        <v>-1.655954432478167</v>
       </c>
       <c r="G9">
-        <v>-7.67160116082332</v>
+        <v>-8.960171422164922</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.41975112939938</v>
       </c>
       <c r="E10">
-        <v>-16.29831513738979</v>
+        <v>-14.03895530006087</v>
       </c>
       <c r="F10">
-        <v>-0.6784594673506309</v>
+        <v>-2.074173155803754</v>
       </c>
       <c r="G10">
-        <v>-7.359145251735827</v>
+        <v>-8.537567041894798</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.11083733988463</v>
       </c>
       <c r="E11">
-        <v>-17.14327857400699</v>
+        <v>-15.07989297783402</v>
       </c>
       <c r="F11">
-        <v>-0.7676917934501511</v>
+        <v>-1.773354551989693</v>
       </c>
       <c r="G11">
-        <v>-6.273504810860469</v>
+        <v>-8.774747766510343</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.82787501874885</v>
       </c>
       <c r="E12">
-        <v>-18.10678840319699</v>
+        <v>-15.89020453134453</v>
       </c>
       <c r="F12">
-        <v>-0.5183903512123774</v>
+        <v>-1.524624035734435</v>
       </c>
       <c r="G12">
-        <v>-6.582014549665151</v>
+        <v>-8.171271730702138</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.59069857587872</v>
       </c>
       <c r="E13">
-        <v>-17.96139268823272</v>
+        <v>-15.78550168381318</v>
       </c>
       <c r="F13">
-        <v>-0.5331908748451167</v>
+        <v>-1.551996016923933</v>
       </c>
       <c r="G13">
-        <v>-5.421082371590149</v>
+        <v>-8.59783221289169</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.42539212561713</v>
       </c>
       <c r="E14">
-        <v>-18.37245133085697</v>
+        <v>-18.55219099269542</v>
       </c>
       <c r="F14">
-        <v>-0.3957275769438459</v>
+        <v>-1.261884848804158</v>
       </c>
       <c r="G14">
-        <v>-5.384199583737129</v>
+        <v>-7.538927737791488</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.34196728974659</v>
       </c>
       <c r="E15">
-        <v>-19.92674135061364</v>
+        <v>-17.2709860694973</v>
       </c>
       <c r="F15">
-        <v>-0.1505889057048047</v>
+        <v>-0.9343974292270537</v>
       </c>
       <c r="G15">
-        <v>-5.506054143946622</v>
+        <v>-6.093692529894954</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.33154943286139</v>
       </c>
       <c r="E16">
-        <v>-20.16783730678201</v>
+        <v>-17.43087742976013</v>
       </c>
       <c r="F16">
-        <v>0.3930617016824602</v>
+        <v>-0.7049390302567785</v>
       </c>
       <c r="G16">
-        <v>-5.1683818094865</v>
+        <v>-6.283562248208775</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.36901613256103</v>
       </c>
       <c r="E17">
-        <v>-21.81025143072794</v>
+        <v>-19.7596995298927</v>
       </c>
       <c r="F17">
-        <v>0.3067885300859386</v>
+        <v>-0.912133691467806</v>
       </c>
       <c r="G17">
-        <v>-4.658153909882946</v>
+        <v>-5.942731653304189</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.42077314739659</v>
       </c>
       <c r="E18">
-        <v>-22.23785258890221</v>
+        <v>-20.98438004052707</v>
       </c>
       <c r="F18">
-        <v>0.4428882571940161</v>
+        <v>-0.8755698811450977</v>
       </c>
       <c r="G18">
-        <v>-4.010743624223073</v>
+        <v>-6.05669387294806</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.45319100036671</v>
       </c>
       <c r="E19">
-        <v>-23.28328251289097</v>
+        <v>-20.97253808099702</v>
       </c>
       <c r="F19">
-        <v>0.8279948572395956</v>
+        <v>-0.1310982370034914</v>
       </c>
       <c r="G19">
-        <v>-3.715552210122879</v>
+        <v>-4.830620090296819</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.43881313797606</v>
       </c>
       <c r="E20">
-        <v>-23.99948331957407</v>
+        <v>-22.59472351155068</v>
       </c>
       <c r="F20">
-        <v>0.7192766135565085</v>
+        <v>-0.1526762301013539</v>
       </c>
       <c r="G20">
-        <v>-4.153696291154342</v>
+        <v>-4.050119252867165</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.3666903162115</v>
       </c>
       <c r="E21">
-        <v>-24.48978120038454</v>
+        <v>-22.79750857761416</v>
       </c>
       <c r="F21">
-        <v>1.105080044204881</v>
+        <v>0.3027231570010055</v>
       </c>
       <c r="G21">
-        <v>-3.396372583045126</v>
+        <v>-4.628991314227507</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-12.2317386132152</v>
       </c>
       <c r="E22">
-        <v>-25.72830525606036</v>
+        <v>-23.77130257127558</v>
       </c>
       <c r="F22">
-        <v>1.281039273645697</v>
+        <v>0.1372345992201182</v>
       </c>
       <c r="G22">
-        <v>-3.61589154720866</v>
+        <v>-4.143347525798581</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-12.03489527865674</v>
       </c>
       <c r="E23">
-        <v>-25.48084226543721</v>
+        <v>-23.19508595311758</v>
       </c>
       <c r="F23">
-        <v>1.658021462345072</v>
+        <v>0.1560157676713146</v>
       </c>
       <c r="G23">
-        <v>-3.312380732168277</v>
+        <v>-4.501641248422823</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.78352498650413</v>
       </c>
       <c r="E24">
-        <v>-25.82224844934948</v>
+        <v>-24.40638482305928</v>
       </c>
       <c r="F24">
-        <v>1.58237099817636</v>
+        <v>0.04878066457803649</v>
       </c>
       <c r="G24">
-        <v>-4.005870501189266</v>
+        <v>-4.131757305865593</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.49135228904799</v>
       </c>
       <c r="E25">
-        <v>-26.19779027033158</v>
+        <v>-25.89456817925198</v>
       </c>
       <c r="F25">
-        <v>1.350944052753194</v>
+        <v>0.1787284860575895</v>
       </c>
       <c r="G25">
-        <v>-3.84069414205287</v>
+        <v>-4.356245398883572</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.17444533967905</v>
       </c>
       <c r="E26">
-        <v>-26.41604913207927</v>
+        <v>-25.8311152014565</v>
       </c>
       <c r="F26">
-        <v>1.428699262083524</v>
+        <v>-0.05720331084204449</v>
       </c>
       <c r="G26">
-        <v>-4.155715723933298</v>
+        <v>-4.268870170465587</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.85044919763272</v>
       </c>
       <c r="E27">
-        <v>-26.95458431801944</v>
+        <v>-25.86484327586563</v>
       </c>
       <c r="F27">
-        <v>1.286254417225239</v>
+        <v>0.1773562048818612</v>
       </c>
       <c r="G27">
-        <v>-4.324781974078338</v>
+        <v>-4.501704148788069</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.53659900208178</v>
       </c>
       <c r="E28">
-        <v>-26.40401244816688</v>
+        <v>-24.81016620795321</v>
       </c>
       <c r="F28">
-        <v>1.273182508599201</v>
+        <v>-0.09009925826459497</v>
       </c>
       <c r="G28">
-        <v>-3.695808116526666</v>
+        <v>-4.225677482814716</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.24391597593133</v>
       </c>
       <c r="E29">
-        <v>-26.99328012841498</v>
+        <v>-26.1710586882643</v>
       </c>
       <c r="F29">
-        <v>1.28485442119599</v>
+        <v>0.09679229311049878</v>
       </c>
       <c r="G29">
-        <v>-3.524384757957665</v>
+        <v>-4.751147134081075</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.978073121912974</v>
       </c>
       <c r="E30">
-        <v>-26.6941381924163</v>
+        <v>-26.03389121057197</v>
       </c>
       <c r="F30">
-        <v>1.346867593726853</v>
+        <v>-0.009650165172101925</v>
       </c>
       <c r="G30">
-        <v>-3.277328675998474</v>
+        <v>-4.288670543335968</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.739209276796117</v>
       </c>
       <c r="E31">
-        <v>-26.79280458409542</v>
+        <v>-25.72753541547906</v>
       </c>
       <c r="F31">
-        <v>1.291216167858311</v>
+        <v>0.1161127134259023</v>
       </c>
       <c r="G31">
-        <v>-3.135412209820997</v>
+        <v>-3.760525971273879</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.524006482224408</v>
       </c>
       <c r="E32">
-        <v>-27.07769088391796</v>
+        <v>-24.28345033917306</v>
       </c>
       <c r="F32">
-        <v>1.195964175574205</v>
+        <v>0.1220033075783793</v>
       </c>
       <c r="G32">
-        <v>-3.773801258886356</v>
+        <v>-3.714085638448982</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.324349334243179</v>
       </c>
       <c r="E33">
-        <v>-26.59090257046343</v>
+        <v>-25.16963194620808</v>
       </c>
       <c r="F33">
-        <v>1.268588177738512</v>
+        <v>-0.1117849433647073</v>
       </c>
       <c r="G33">
-        <v>-2.831812010051054</v>
+        <v>-3.910205666740947</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.134337315375573</v>
       </c>
       <c r="E34">
-        <v>-27.56200212209029</v>
+        <v>-24.7155211011929</v>
       </c>
       <c r="F34">
-        <v>1.166401137250697</v>
+        <v>-0.1474428739037842</v>
       </c>
       <c r="G34">
-        <v>-2.802036963470849</v>
+        <v>-3.537590524113817</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.947577482972649</v>
       </c>
       <c r="E35">
-        <v>-25.36245889792869</v>
+        <v>-24.98175461657785</v>
       </c>
       <c r="F35">
-        <v>1.353291104919875</v>
+        <v>-0.08834292840437263</v>
       </c>
       <c r="G35">
-        <v>-2.880357849838926</v>
+        <v>-3.277295570543081</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.759106063805559</v>
       </c>
       <c r="E36">
-        <v>-25.73820902871514</v>
+        <v>-25.54686741646904</v>
       </c>
       <c r="F36">
-        <v>1.001901603814001</v>
+        <v>0.09073145057211202</v>
       </c>
       <c r="G36">
-        <v>-2.380928949784475</v>
+        <v>-2.678229181393185</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.567508046998897</v>
       </c>
       <c r="E37">
-        <v>-25.43303063686422</v>
+        <v>-24.43098802234296</v>
       </c>
       <c r="F37">
-        <v>0.9159507163712717</v>
+        <v>-0.07654907045209507</v>
       </c>
       <c r="G37">
-        <v>-1.529651959270743</v>
+        <v>-2.090024692157638</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.375193135540831</v>
       </c>
       <c r="E38">
-        <v>-25.54846143931974</v>
+        <v>-23.44493997801678</v>
       </c>
       <c r="F38">
-        <v>1.154567686650533</v>
+        <v>0.02661036546779966</v>
       </c>
       <c r="G38">
-        <v>-1.868969634863882</v>
+        <v>-3.568845384550077</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.187364352031979</v>
       </c>
       <c r="E39">
-        <v>-24.84435618671112</v>
+        <v>-23.48334596607583</v>
       </c>
       <c r="F39">
-        <v>1.318048897183601</v>
+        <v>0.03075175643667382</v>
       </c>
       <c r="G39">
-        <v>-1.721643737275236</v>
+        <v>-3.8427367486506</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.007495646087817</v>
       </c>
       <c r="E40">
-        <v>-24.33897848745511</v>
+        <v>-22.40181957577194</v>
       </c>
       <c r="F40">
-        <v>1.159391654868962</v>
+        <v>0.3117075206592935</v>
       </c>
       <c r="G40">
-        <v>-2.188728607411008</v>
+        <v>-2.652032834540932</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.841166037501782</v>
       </c>
       <c r="E41">
-        <v>-24.60462330121906</v>
+        <v>-23.70501929722531</v>
       </c>
       <c r="F41">
-        <v>1.098941600076638</v>
+        <v>0.3686053230832866</v>
       </c>
       <c r="G41">
-        <v>-2.001348419342719</v>
+        <v>-2.952686648780924</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.688750018265619</v>
       </c>
       <c r="E42">
-        <v>-24.01322723818735</v>
+        <v>-23.45385201486388</v>
       </c>
       <c r="F42">
-        <v>1.385019069229789</v>
+        <v>0.5188340825159571</v>
       </c>
       <c r="G42">
-        <v>-2.736044548691017</v>
+        <v>-2.979670905471523</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.548573564772235</v>
       </c>
       <c r="E43">
-        <v>-24.78530941412511</v>
+        <v>-22.08181043154591</v>
       </c>
       <c r="F43">
-        <v>1.362579540113928</v>
+        <v>0.4258903416036046</v>
       </c>
       <c r="G43">
-        <v>-2.226849539295716</v>
+        <v>-3.474518010499623</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.416766856223937</v>
       </c>
       <c r="E44">
-        <v>-23.94229322133121</v>
+        <v>-22.11355956281368</v>
       </c>
       <c r="F44">
-        <v>1.274641101747321</v>
+        <v>0.3754714800796743</v>
       </c>
       <c r="G44">
-        <v>-2.352332457416251</v>
+        <v>-3.345449771560057</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.288878247017483</v>
       </c>
       <c r="E45">
-        <v>-23.39932013086351</v>
+        <v>-21.29539110689986</v>
       </c>
       <c r="F45">
-        <v>0.9877971189310977</v>
+        <v>0.5343623190168409</v>
       </c>
       <c r="G45">
-        <v>-2.044925130276146</v>
+        <v>-3.845428222174027</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.162882821528383</v>
       </c>
       <c r="E46">
-        <v>-23.05641955052871</v>
+        <v>-20.80909186863817</v>
       </c>
       <c r="F46">
-        <v>1.030264193053607</v>
+        <v>0.5793419425741944</v>
       </c>
       <c r="G46">
-        <v>-2.964257005440676</v>
+        <v>-3.750988289575238</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.040416388134736</v>
       </c>
       <c r="E47">
-        <v>-22.23228709434678</v>
+        <v>-21.13236151414972</v>
       </c>
       <c r="F47">
-        <v>1.214859370851313</v>
+        <v>0.1877643201581292</v>
       </c>
       <c r="G47">
-        <v>-2.897254874271367</v>
+        <v>-4.074508041854975</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.93118967235158</v>
       </c>
       <c r="E48">
-        <v>-22.50201206319165</v>
+        <v>-20.48617544409921</v>
       </c>
       <c r="F48">
-        <v>1.375114572434631</v>
+        <v>0.2245759804566038</v>
       </c>
       <c r="G48">
-        <v>-2.059147233912855</v>
+        <v>-4.267155307876244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.845120984830797</v>
       </c>
       <c r="E49">
-        <v>-22.35211051658974</v>
+        <v>-19.96959882862223</v>
       </c>
       <c r="F49">
-        <v>1.622345319187967</v>
+        <v>0.3957896351218047</v>
       </c>
       <c r="G49">
-        <v>-2.461802266763331</v>
+        <v>-4.691107080180852</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.79098346440114</v>
       </c>
       <c r="E50">
-        <v>-21.63977702670919</v>
+        <v>-18.74191141124676</v>
       </c>
       <c r="F50">
-        <v>1.081441649711032</v>
+        <v>0.8123161686767452</v>
       </c>
       <c r="G50">
-        <v>-2.756824843041022</v>
+        <v>-4.907858428273554</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.775186885348161</v>
       </c>
       <c r="E51">
-        <v>-21.1639340349312</v>
+        <v>-18.87348169506562</v>
       </c>
       <c r="F51">
-        <v>1.367463689157143</v>
+        <v>-0.007660238689352259</v>
       </c>
       <c r="G51">
-        <v>-3.366594225919382</v>
+        <v>-3.702498729061533</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.801806255388307</v>
       </c>
       <c r="E52">
-        <v>-21.54913056249765</v>
+        <v>-19.9810920956537</v>
       </c>
       <c r="F52">
-        <v>1.274337030211557</v>
+        <v>1.034592461320502</v>
       </c>
       <c r="G52">
-        <v>-3.551090928822966</v>
+        <v>-4.846662993980127</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.871328989166751</v>
       </c>
       <c r="E53">
-        <v>-20.05632816281713</v>
+        <v>-19.4894220872189</v>
       </c>
       <c r="F53">
-        <v>0.9602390522965358</v>
+        <v>0.6329488041059043</v>
       </c>
       <c r="G53">
-        <v>-3.448540159652962</v>
+        <v>-4.674041217925909</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.983489030837729</v>
       </c>
       <c r="E54">
-        <v>-20.39784303010559</v>
+        <v>-18.84704899228285</v>
       </c>
       <c r="F54">
-        <v>1.248269230843424</v>
+        <v>0.4807863397504821</v>
       </c>
       <c r="G54">
-        <v>-3.453059054314067</v>
+        <v>-4.377790429253149</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.137368165001038</v>
       </c>
       <c r="E55">
-        <v>-20.92169237483889</v>
+        <v>-17.04720246946026</v>
       </c>
       <c r="F55">
-        <v>1.335678711434273</v>
+        <v>0.2456345180142021</v>
       </c>
       <c r="G55">
-        <v>-3.630120271936447</v>
+        <v>-3.861656516407535</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.328913237645126</v>
       </c>
       <c r="E56">
-        <v>-20.2449979753987</v>
+        <v>-18.26521253788133</v>
       </c>
       <c r="F56">
-        <v>0.917068812747572</v>
+        <v>0.4557685374042852</v>
       </c>
       <c r="G56">
-        <v>-3.562830123305221</v>
+        <v>-4.875097269616927</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.5533374459996</v>
       </c>
       <c r="E57">
-        <v>-19.18895783680998</v>
+        <v>-18.13011004433649</v>
       </c>
       <c r="F57">
-        <v>1.312735563837302</v>
+        <v>0.2630639934665709</v>
       </c>
       <c r="G57">
-        <v>-4.034417335374402</v>
+        <v>-4.813620438952661</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.805886469043886</v>
       </c>
       <c r="E58">
-        <v>-19.79180188213308</v>
+        <v>-18.18535742723007</v>
       </c>
       <c r="F58">
-        <v>1.047081566169658</v>
+        <v>0.05496582803078525</v>
       </c>
       <c r="G58">
-        <v>-3.863560080092616</v>
+        <v>-5.619235074843226</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.082167653616636</v>
       </c>
       <c r="E59">
-        <v>-18.49045883502285</v>
+        <v>-16.45237835160474</v>
       </c>
       <c r="F59">
-        <v>1.27227662881557</v>
+        <v>0.1866802734590109</v>
       </c>
       <c r="G59">
-        <v>-3.998848834100472</v>
+        <v>-5.030762431418998</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.376117387215311</v>
       </c>
       <c r="E60">
-        <v>-18.05468830973874</v>
+        <v>-16.47713551900467</v>
       </c>
       <c r="F60">
-        <v>0.9686944581790671</v>
+        <v>0.3898689505569343</v>
       </c>
       <c r="G60">
-        <v>-4.395435636977464</v>
+        <v>-6.058246518805978</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.685314146289851</v>
       </c>
       <c r="E61">
-        <v>-18.68073172740314</v>
+        <v>-16.58522566509376</v>
       </c>
       <c r="F61">
-        <v>1.148730146646223</v>
+        <v>0.01658233961123708</v>
       </c>
       <c r="G61">
-        <v>-4.678497212221768</v>
+        <v>-5.488975039509523</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.006006811299519</v>
       </c>
       <c r="E62">
-        <v>-18.90389945497514</v>
+        <v>-16.20226167521309</v>
       </c>
       <c r="F62">
-        <v>1.126518671182185</v>
+        <v>0.04753745543441652</v>
       </c>
       <c r="G62">
-        <v>-5.013842233167782</v>
+        <v>-6.264380947354238</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.333248212050089</v>
       </c>
       <c r="E63">
-        <v>-17.39587685415484</v>
+        <v>-17.00000671335232</v>
       </c>
       <c r="F63">
-        <v>1.220684241208299</v>
+        <v>0.007528292892669762</v>
       </c>
       <c r="G63">
-        <v>-5.033596258400613</v>
+        <v>-6.435152128452002</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.661866396536489</v>
       </c>
       <c r="E64">
-        <v>-18.03611250935928</v>
+        <v>-15.31257050082213</v>
       </c>
       <c r="F64">
-        <v>0.9942222138300355</v>
+        <v>-0.07659816533547369</v>
       </c>
       <c r="G64">
-        <v>-5.376870035913182</v>
+        <v>-6.865380695099068</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.986944374791324</v>
       </c>
       <c r="E65">
-        <v>-17.35155215056777</v>
+        <v>-15.19383391234101</v>
       </c>
       <c r="F65">
-        <v>1.007175344512415</v>
+        <v>-0.1428263711602782</v>
       </c>
       <c r="G65">
-        <v>-5.050062911912948</v>
+        <v>-6.074918426141748</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.30352965704773</v>
       </c>
       <c r="E66">
-        <v>-18.01060361527407</v>
+        <v>-14.64346582381879</v>
       </c>
       <c r="F66">
-        <v>0.8935634495506197</v>
+        <v>-0.03909363369899441</v>
       </c>
       <c r="G66">
-        <v>-5.586182588179142</v>
+        <v>-6.334577754968944</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.60255975444393</v>
       </c>
       <c r="E67">
-        <v>-17.58130880782093</v>
+        <v>-14.69317035452698</v>
       </c>
       <c r="F67">
-        <v>1.077616999925246</v>
+        <v>-0.1402861068719133</v>
       </c>
       <c r="G67">
-        <v>-5.656594581253901</v>
+        <v>-7.420261232936312</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.87794116411721</v>
       </c>
       <c r="E68">
-        <v>-16.80873755669034</v>
+        <v>-15.02016693414685</v>
       </c>
       <c r="F68">
-        <v>1.038665752935013</v>
+        <v>-0.5417436786414475</v>
       </c>
       <c r="G68">
-        <v>-6.2150372660914</v>
+        <v>-7.162859696166898</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.12127970262519</v>
       </c>
       <c r="E69">
-        <v>-17.7344980265524</v>
+        <v>-15.8815098612498</v>
       </c>
       <c r="F69">
-        <v>0.5727046310825876</v>
+        <v>-0.1797045471072012</v>
       </c>
       <c r="G69">
-        <v>-6.258577561023896</v>
+        <v>-7.214537312034921</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.32773651768114</v>
       </c>
       <c r="E70">
-        <v>-17.98233235204419</v>
+        <v>-15.05806573311704</v>
       </c>
       <c r="F70">
-        <v>0.8516981836759779</v>
+        <v>-0.4619890405928746</v>
       </c>
       <c r="G70">
-        <v>-6.073220116280101</v>
+        <v>-6.643110667592401</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.49616354596963</v>
       </c>
       <c r="E71">
-        <v>-17.00669526946164</v>
+        <v>-14.84677166439315</v>
       </c>
       <c r="F71">
-        <v>0.4391863446166764</v>
+        <v>-0.3528194407238872</v>
       </c>
       <c r="G71">
-        <v>-6.12805268204705</v>
+        <v>-7.146071919737254</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.62781267192903</v>
       </c>
       <c r="E72">
-        <v>-18.5045378607127</v>
+        <v>-15.60490161191328</v>
       </c>
       <c r="F72">
-        <v>0.4370293371598479</v>
+        <v>-0.4550397390359263</v>
       </c>
       <c r="G72">
-        <v>-6.786364594167743</v>
+        <v>-8.496777810305439</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.72419293459507</v>
       </c>
       <c r="E73">
-        <v>-16.97960140947375</v>
+        <v>-15.45255468934723</v>
       </c>
       <c r="F73">
-        <v>0.5897421393208853</v>
+        <v>-0.4207168725835649</v>
       </c>
       <c r="G73">
-        <v>-7.009813175886391</v>
+        <v>-8.079311396712262</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.78644994730419</v>
       </c>
       <c r="E74">
-        <v>-17.9951524619599</v>
+        <v>-15.02236777251458</v>
       </c>
       <c r="F74">
-        <v>0.5189742404894735</v>
+        <v>-0.6707903714551154</v>
       </c>
       <c r="G74">
-        <v>-6.854220846086185</v>
+        <v>-7.861100098036742</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.81766691064703</v>
       </c>
       <c r="E75">
-        <v>-17.08055920900076</v>
+        <v>-15.29654423130898</v>
       </c>
       <c r="F75">
-        <v>0.6791613427184273</v>
+        <v>-0.434444435458594</v>
       </c>
       <c r="G75">
-        <v>-7.426028203265722</v>
+        <v>-7.784454347711535</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.81590846666963</v>
       </c>
       <c r="E76">
-        <v>-17.97239235159735</v>
+        <v>-16.14877134023449</v>
       </c>
       <c r="F76">
-        <v>0.4177619709926116</v>
+        <v>-0.8121424592317479</v>
       </c>
       <c r="G76">
-        <v>-6.538937731108154</v>
+        <v>-8.689497908328571</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.77719288718025</v>
       </c>
       <c r="E77">
-        <v>-18.69067172784997</v>
+        <v>-16.63469018667954</v>
       </c>
       <c r="F77">
-        <v>0.3978793350772271</v>
+        <v>-0.4693564405114989</v>
       </c>
       <c r="G77">
-        <v>-7.384139870557324</v>
+        <v>-8.227213329224742</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.69698622055475</v>
       </c>
       <c r="E78">
-        <v>-18.82110989316691</v>
+        <v>-17.10519863607649</v>
       </c>
       <c r="F78">
-        <v>0.274805589123639</v>
+        <v>-0.7192794873210827</v>
       </c>
       <c r="G78">
-        <v>-7.254138057775684</v>
+        <v>-8.379495113485678</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.57195910637279</v>
       </c>
       <c r="E79">
-        <v>-19.37975603217515</v>
+        <v>-17.67286549530801</v>
       </c>
       <c r="F79">
-        <v>0.2033796604843622</v>
+        <v>-0.3925704592014173</v>
       </c>
       <c r="G79">
-        <v>-6.9615354902872</v>
+        <v>-7.775380142388393</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.39925282842909</v>
       </c>
       <c r="E80">
-        <v>-19.93366991584537</v>
+        <v>-17.28628778316922</v>
       </c>
       <c r="F80">
-        <v>0.424818172698852</v>
+        <v>-0.6274744309619311</v>
       </c>
       <c r="G80">
-        <v>-7.780504866883184</v>
+        <v>-7.79974244701189</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.18204399833664</v>
       </c>
       <c r="E81">
-        <v>-20.08958980440347</v>
+        <v>-18.96262470590661</v>
       </c>
       <c r="F81">
-        <v>0.1558684830211788</v>
+        <v>-0.8291752163522991</v>
       </c>
       <c r="G81">
-        <v>-7.528625320073275</v>
+        <v>-8.522974157157691</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.92918633162635</v>
       </c>
       <c r="E82">
-        <v>-21.17064976188458</v>
+        <v>-19.88243476092259</v>
       </c>
       <c r="F82">
-        <v>0.2708249443051819</v>
+        <v>-0.4427375114847927</v>
       </c>
       <c r="G82">
-        <v>-7.048109566684681</v>
+        <v>-8.494463738973486</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.65285909155361</v>
       </c>
       <c r="E83">
-        <v>-21.84927329125203</v>
+        <v>-20.41406855247508</v>
       </c>
       <c r="F83">
-        <v>0.2771486820255317</v>
+        <v>-0.4610879119269896</v>
       </c>
       <c r="G83">
-        <v>-7.378465595503013</v>
+        <v>-7.878079886107663</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.36814806097528</v>
       </c>
       <c r="E84">
-        <v>-22.50690734359394</v>
+        <v>-21.06181241758423</v>
       </c>
       <c r="F84">
-        <v>0.5938376028182116</v>
+        <v>-0.5191085618450292</v>
       </c>
       <c r="G84">
-        <v>-7.234642255094916</v>
+        <v>-7.54968370024858</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.08978990603214</v>
       </c>
       <c r="E85">
-        <v>-23.60210519692699</v>
+        <v>-21.59383565790137</v>
       </c>
       <c r="F85">
-        <v>-0.01575376777020555</v>
+        <v>-0.7792085028672269</v>
       </c>
       <c r="G85">
-        <v>-7.41472600079465</v>
+        <v>-7.812398662608524</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.830108919318706</v>
       </c>
       <c r="E86">
-        <v>-24.02956144393302</v>
+        <v>-22.22618723985845</v>
       </c>
       <c r="F86">
-        <v>0.4385243555440227</v>
+        <v>-0.5932093697754832</v>
       </c>
       <c r="G86">
-        <v>-7.095096139523557</v>
+        <v>-8.064311314873825</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.594709704203073</v>
       </c>
       <c r="E87">
-        <v>-26.24800651860264</v>
+        <v>-23.57660083131579</v>
       </c>
       <c r="F87">
-        <v>-0.01240185420017796</v>
+        <v>-1.028476687280776</v>
       </c>
       <c r="G87">
-        <v>-7.317296645573899</v>
+        <v>-7.881075929820704</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.389420492276356</v>
       </c>
       <c r="E88">
-        <v>-28.0643095159691</v>
+        <v>-25.25166072438302</v>
       </c>
       <c r="F88">
-        <v>0.421628588985157</v>
+        <v>-0.3462621063810102</v>
       </c>
       <c r="G88">
-        <v>-7.119001588862634</v>
+        <v>-7.273110794261247</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.214594576590494</v>
       </c>
       <c r="E89">
-        <v>-29.07260142462095</v>
+        <v>-27.09239483902087</v>
       </c>
       <c r="F89">
-        <v>0.2900669711777712</v>
+        <v>-0.4808406839573081</v>
       </c>
       <c r="G89">
-        <v>-7.201424241153869</v>
+        <v>-7.788681914365185</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.068353232396058</v>
       </c>
       <c r="E90">
-        <v>-30.26976239871071</v>
+        <v>-26.40812430256585</v>
       </c>
       <c r="F90">
-        <v>0.5750215928368756</v>
+        <v>-0.5800186832057881</v>
       </c>
       <c r="G90">
-        <v>-6.438283904532153</v>
+        <v>-8.408958968785191</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.9493107330571</v>
       </c>
       <c r="E91">
-        <v>-32.06609256146635</v>
+        <v>-30.65266751842928</v>
       </c>
       <c r="F91">
-        <v>0.523419702994112</v>
+        <v>-0.3924097130510002</v>
       </c>
       <c r="G91">
-        <v>-6.987589483681264</v>
+        <v>-7.843153630668352</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.858233508091507</v>
       </c>
       <c r="E92">
-        <v>-34.26103032756215</v>
+        <v>-31.00110642247547</v>
       </c>
       <c r="F92">
-        <v>0.5003870760129184</v>
+        <v>-0.5768409772864588</v>
       </c>
       <c r="G92">
-        <v>-7.044484519319179</v>
+        <v>-6.843004717799134</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.800131885771867</v>
       </c>
       <c r="E93">
-        <v>-36.91604973165224</v>
+        <v>-34.05712219994476</v>
       </c>
       <c r="F93">
-        <v>0.6868898275857718</v>
+        <v>-0.2324958000924597</v>
       </c>
       <c r="G93">
-        <v>-7.182216455935017</v>
+        <v>-8.168749095001212</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.781696513358456</v>
       </c>
       <c r="E94">
-        <v>-38.38474027147891</v>
+        <v>-35.91000168187118</v>
       </c>
       <c r="F94">
-        <v>0.6356094300438425</v>
+        <v>-0.0008202128405692856</v>
       </c>
       <c r="G94">
-        <v>-6.828183405419817</v>
+        <v>-6.485104950094065</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.814561731175612</v>
       </c>
       <c r="E95">
-        <v>-40.11732310562857</v>
+        <v>-40.01744081867839</v>
       </c>
       <c r="F95">
-        <v>0.7649586106873594</v>
+        <v>-0.2645547589387005</v>
       </c>
       <c r="G95">
-        <v>-6.719422052818141</v>
+        <v>-7.115217635311247</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.904525708996998</v>
       </c>
       <c r="E96">
-        <v>-42.830990776592</v>
+        <v>-40.74938260101216</v>
       </c>
       <c r="F96">
-        <v>1.471000047084912</v>
+        <v>0.2751318325422195</v>
       </c>
       <c r="G96">
-        <v>-6.37806508117281</v>
+        <v>-7.152272571532309</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.045663406223362</v>
       </c>
       <c r="E97">
-        <v>-45.70516115180929</v>
+        <v>-42.29782636082492</v>
       </c>
       <c r="F97">
-        <v>1.110249260312876</v>
+        <v>0.2450651757376016</v>
       </c>
       <c r="G97">
-        <v>-7.201861233165053</v>
+        <v>-7.171010259284584</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.231642590187839</v>
       </c>
       <c r="E98">
-        <v>-47.3552419822502</v>
+        <v>-45.1953093202337</v>
       </c>
       <c r="F98">
-        <v>1.17196311242572</v>
+        <v>0.3999167727374399</v>
       </c>
       <c r="G98">
-        <v>-6.492302076096441</v>
+        <v>-7.535524496977117</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.439550170750369</v>
       </c>
       <c r="E99">
-        <v>-49.83248934645818</v>
+        <v>-46.98288141425849</v>
       </c>
       <c r="F99">
-        <v>1.214539462256394</v>
+        <v>0.2979815414901799</v>
       </c>
       <c r="G99">
-        <v>-6.708765406727227</v>
+        <v>-7.672958484494421</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.660386204301441</v>
       </c>
       <c r="E100">
-        <v>-52.60773747121491</v>
+        <v>-49.73925938782526</v>
       </c>
       <c r="F100">
-        <v>1.651658131976836</v>
+        <v>0.3056229225321752</v>
       </c>
       <c r="G100">
-        <v>-7.670849666985905</v>
+        <v>-8.039869557157386</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.857881753826303</v>
       </c>
       <c r="E101">
-        <v>-53.8093420104247</v>
+        <v>-51.98110648404802</v>
       </c>
       <c r="F101">
-        <v>1.49407622597878</v>
+        <v>0.5821530205740993</v>
       </c>
       <c r="G101">
-        <v>-7.819887116618355</v>
+        <v>-7.462480620198638</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.04685020448133</v>
       </c>
       <c r="E102">
-        <v>-56.37298360175101</v>
+        <v>-54.60408919877084</v>
       </c>
       <c r="F102">
-        <v>1.723672407363699</v>
+        <v>0.7938802481151146</v>
       </c>
       <c r="G102">
-        <v>-7.854866340786294</v>
+        <v>-7.774320767815826</v>
       </c>
     </row>
   </sheetData>
